--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105354_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105354_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2963</v>
+        <v>3.2926</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1009</v>
+        <v>5.1334</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8046</v>
+        <v>-1.8408</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7719</v>
+        <v>-0.8072</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5291</v>
+        <v>1.5874</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.301</v>
+        <v>-2.3946</v>
       </c>
       <c r="J2" t="n">
-        <v>1.141</v>
+        <v>1.2664</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0302</v>
+        <v>1.1553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1108</v>
+        <v>0.1112</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9129</v>
+        <v>-2.0736</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4989</v>
+        <v>0.4322</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.4118</v>
+        <v>-2.5058</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1526</v>
+        <v>1.1618</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5133</v>
+        <v>0.3847</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6392</v>
+        <v>0.7772</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3772</v>
+        <v>3.3969</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6004</v>
+        <v>4.6298</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7755</v>
+        <v>2.791</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4867</v>
+        <v>2.5786</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2887</v>
+        <v>0.2124</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1704</v>
+        <v>-0.1257</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6868</v>
+        <v>0.7702</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8572</v>
+        <v>-0.8959</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3771</v>
+        <v>1.6126</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6966</v>
+        <v>0.8583</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6805</v>
+        <v>0.7543</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5475</v>
+        <v>-1.7384</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0098</v>
+        <v>-0.0881</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5377</v>
+        <v>-1.6502</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4844</v>
+        <v>0.4577</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0326</v>
+        <v>-0.1161</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4517</v>
+        <v>0.5737</v>
       </c>
       <c r="V3" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W3" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,58 +736,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.4649</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9129</v>
+        <v>1.8946</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4129</v>
+        <v>-0.4297</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6011</v>
+        <v>0.5313</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0764</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5174</v>
+        <v>0.4548</v>
       </c>
       <c r="J4" t="n">
-        <v>1.908</v>
+        <v>1.952</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4182</v>
+        <v>-0.3822</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3262</v>
+        <v>2.3342</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.307</v>
+        <v>-1.4207</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5019</v>
+        <v>0.4586</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8088</v>
+        <v>-1.8793</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2067</v>
+        <v>0.2451</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0049</v>
+        <v>-0.0574</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2018</v>
+        <v>0.3025</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0772</v>
+        <v>1.0667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3545</v>
+        <v>0.3879</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7228</v>
+        <v>0.6788</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5678</v>
+        <v>-1.5732</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8582</v>
+        <v>-0.8255</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7095</v>
+        <v>-0.7477</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1838</v>
+        <v>-0.0704</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0071</v>
+        <v>0.0711</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1767</v>
+        <v>-0.1415</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.384</v>
+        <v>-1.5027</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8511</v>
+        <v>-0.8966</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.6061</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S5" t="n">
-        <v>0.268</v>
+        <v>0.2595</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6849</v>
+        <v>-0.7745</v>
       </c>
       <c r="U5" t="n">
-        <v>0.953</v>
+        <v>1.034</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7196</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6258</v>
+        <v>1.627</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9062</v>
+        <v>-0.927</v>
       </c>
       <c r="G6" t="n">
-        <v>0.68</v>
+        <v>0.6309</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2703</v>
+        <v>1.2876</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5903</v>
+        <v>-0.6567</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2158</v>
+        <v>1.2635</v>
       </c>
       <c r="K6" t="n">
-        <v>1.105</v>
+        <v>1.1524</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1108</v>
+        <v>0.1112</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1653</v>
+        <v>0.1352</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.7678</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6923</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7319</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4868</v>
+        <v>0.429</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2451</v>
+        <v>0.3286</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5568</v>
+        <v>0.5172</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3904</v>
+        <v>0.4019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1664</v>
+        <v>0.1153</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7005</v>
+        <v>-0.7186</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1325</v>
+        <v>0.11</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8329</v>
+        <v>-0.8286</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6498</v>
+        <v>0.7281</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1509</v>
+        <v>1.1594</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5011</v>
+        <v>-0.4313</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3503</v>
+        <v>-1.4468</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0184</v>
+        <v>-1.0495</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3318</v>
+        <v>-0.3973</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R7" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4111</v>
+        <v>0.3834</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1826</v>
+        <v>-0.2608</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5936</v>
+        <v>0.6442</v>
       </c>
       <c r="V7" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W7" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,40 +1068,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1122</v>
+        <v>-0.1179</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2218</v>
+        <v>-0.2244</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1097</v>
+        <v>0.1065</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6518</v>
+        <v>-0.6616</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7915</v>
+        <v>-0.7661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1398</v>
+        <v>0.1045</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2459</v>
+        <v>-0.2087</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2828</v>
+        <v>-0.2458</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4059</v>
+        <v>-0.4529</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5087</v>
+        <v>-0.5203</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1028</v>
+        <v>0.0674</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5396</v>
+        <v>0.5437</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0241</v>
+        <v>-0.0156</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5155</v>
+        <v>0.5594</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7947</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8913</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1069</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2879</v>
+        <v>0.268</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3206</v>
+        <v>0.3151</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0327</v>
+        <v>-0.0471</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3216</v>
+        <v>0.324</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3216</v>
+        <v>0.324</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0337</v>
+        <v>-0.0559</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.001</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0327</v>
+        <v>-0.0471</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0781</v>
+        <v>0.0848</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0625</v>
+        <v>-0.0678</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1406</v>
+        <v>0.1526</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5761</v>
+        <v>-1.5702</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4879</v>
+        <v>-1.4055</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0882</v>
+        <v>-0.1647</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9873</v>
+        <v>-3.9271</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4533</v>
+        <v>-2.3307</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.534</v>
+        <v>-1.5964</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2034</v>
+        <v>-2.0244</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2772</v>
+        <v>-2.0985</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.784</v>
+        <v>-1.9027</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1761</v>
+        <v>-0.2322</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6078</v>
+        <v>-1.6705</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4652</v>
+        <v>0.416</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2847</v>
+        <v>-0.3977</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7499</v>
+        <v>0.8137</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7153</v>
+        <v>1.7114</v>
       </c>
       <c r="W10" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4386</v>
+        <v>-0.4526</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8083</v>
+        <v>-1.8794</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8828</v>
+        <v>-1.9168</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0745</v>
+        <v>0.0373</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3796</v>
+        <v>-0.4472</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1543</v>
+        <v>-0.1711</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2253</v>
+        <v>-0.2761</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4293</v>
+        <v>0.4322</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3554</v>
+        <v>0.3581</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8088</v>
+        <v>-0.8793</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5097</v>
+        <v>-0.5291</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2991</v>
+        <v>-0.3502</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6923</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0481</v>
+        <v>0.0365</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3737</v>
+        <v>-0.4212</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4218</v>
+        <v>0.4577</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7846</v>
+        <v>-0.7803</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7846</v>
+        <v>-0.7803</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2376</v>
+        <v>-2.1723</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1631</v>
+        <v>-2.061</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0745</v>
+        <v>-0.1113</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7964</v>
+        <v>-2.7578</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3248</v>
+        <v>-2.256</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4716</v>
+        <v>-0.5018</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0816</v>
+        <v>-0.8666</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.316</v>
+        <v>-2.1767</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2344</v>
+        <v>1.3101</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7148</v>
+        <v>-1.8912</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0793</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.706</v>
+        <v>-1.8119</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R12" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7896</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0722</v>
+        <v>-0.0469</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7173</v>
+        <v>0.8619</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9547</v>
+        <v>-4.8961</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6433</v>
+        <v>-2.5145</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3114</v>
+        <v>-2.3816</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.082</v>
+        <v>-2.9694</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4543</v>
+        <v>-2.3395</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6277</v>
+        <v>-0.6299</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3923</v>
+        <v>-1.1728</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9282</v>
+        <v>-0.7785</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4641</v>
+        <v>-0.3942</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6897</v>
+        <v>-1.7966</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5262</v>
+        <v>-1.561</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1636</v>
+        <v>-0.2356</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2813</v>
+        <v>0.2373</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1943</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3785</v>
+        <v>0.4316</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.551300000000001</v>
+        <v>-1.598199999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5776</v>
+        <v>3.0099</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.1288</v>
+        <v>-4.6082</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.5387</v>
+        <v>-12.5576</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.013500000000001</v>
+        <v>-4.5422</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.524999999999999</v>
+        <v>-8.015500000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9356</v>
+        <v>3.2359</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5698</v>
+        <v>-0.6031000000000006</v>
       </c>
       <c r="L14" t="n">
-        <v>3.5053</v>
+        <v>3.8393</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.4744</v>
+        <v>-15.7934</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.4437</v>
+        <v>-3.9389</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.0304</v>
+        <v>-11.8544</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0001000000000003221</v>
+        <v>-5.273559366969494e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.230400000000001</v>
+        <v>-9.18</v>
       </c>
       <c r="R14" t="n">
-        <v>9.2302</v>
+        <v>9.18</v>
       </c>
       <c r="S14" t="n">
-        <v>5.4566</v>
+        <v>5.3984</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5517</v>
+        <v>-1.5386</v>
       </c>
       <c r="U14" t="n">
-        <v>6.008</v>
+        <v>6.937100000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>5.531099999999999</v>
+        <v>5.5609</v>
       </c>
       <c r="W14" t="n">
-        <v>10.424</v>
+        <v>10.4924</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.8928</v>
+        <v>-4.9315</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9333</v>
+        <v>7.0887</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4727</v>
+        <v>6.6672</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4606</v>
+        <v>0.4215</v>
       </c>
       <c r="G15" t="n">
-        <v>6.9225</v>
+        <v>7.0821</v>
       </c>
       <c r="H15" t="n">
-        <v>0.65</v>
+        <v>0.7096</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2725</v>
+        <v>6.3725</v>
       </c>
       <c r="J15" t="n">
-        <v>7.0314</v>
+        <v>7.3205</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3243</v>
+        <v>0.4832</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7072</v>
+        <v>6.8373</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1089</v>
+        <v>-0.2383</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3257</v>
+        <v>0.2264</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4347</v>
+        <v>-0.4648</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4507</v>
+        <v>-0.4525</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5587</v>
+        <v>-0.6533</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1081</v>
+        <v>0.2008</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2759</v>
+        <v>3.1126</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9477</v>
+        <v>2.8714</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3282</v>
+        <v>0.2412</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7551</v>
+        <v>4.6128</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9736</v>
+        <v>1.8004</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7815</v>
+        <v>2.8124</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8007</v>
+        <v>4.8925</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9816</v>
+        <v>0.9889</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8191</v>
+        <v>3.9036</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0457</v>
+        <v>-0.2797</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9919</v>
+        <v>0.8115</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0376</v>
+        <v>-1.0912</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R16" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9482</v>
+        <v>-0.9558</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6993</v>
+        <v>-0.8736</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.249</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2272</v>
+        <v>2.3142</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9527</v>
+        <v>3.0995</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7256</v>
+        <v>-0.7853</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2692</v>
+        <v>2.3547</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0687</v>
+        <v>-0.077</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3379</v>
+        <v>2.4317</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7494</v>
+        <v>2.9811</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2806</v>
+        <v>0.361</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4688</v>
+        <v>2.6202</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4801</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3493</v>
+        <v>-0.438</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1309</v>
+        <v>-0.1885</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1958</v>
+        <v>-1.1879</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8736</v>
+        <v>-0.9636</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3222</v>
+        <v>-0.2243</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1207</v>
+        <v>2.0996</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4246</v>
+        <v>1.4211</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6785</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3864</v>
+        <v>2.32</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0251</v>
+        <v>1.9932</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3613</v>
+        <v>0.3268</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1251</v>
+        <v>2.179</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8666</v>
+        <v>1.9196</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2585</v>
+        <v>0.2594</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2613</v>
+        <v>0.141</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1585</v>
+        <v>0.0735</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1028</v>
+        <v>0.0674</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2657</v>
+        <v>-0.2204</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6237</v>
+        <v>-0.6924</v>
       </c>
       <c r="U18" t="n">
-        <v>0.358</v>
+        <v>0.472</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5213</v>
+        <v>0.5042</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2906</v>
+        <v>0.2974</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2307</v>
+        <v>0.2069</v>
       </c>
       <c r="G19" t="n">
-        <v>0.823</v>
+        <v>0.7689</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5821</v>
+        <v>1.5234</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7591</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.728</v>
+        <v>0.772</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4217</v>
+        <v>1.4322</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6936</v>
+        <v>-0.6602</v>
       </c>
       <c r="M19" t="n">
-        <v>0.095</v>
+        <v>-0.0031</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1604</v>
+        <v>0.0912</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0654</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5325</v>
+        <v>-0.4942</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4374</v>
+        <v>-0.4746</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.095</v>
+        <v>-0.0196</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.9539</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3706</v>
+        <v>0.3664</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2642</v>
+        <v>-1.3202</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1136</v>
+        <v>2.0786</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7479</v>
+        <v>0.6439</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3657</v>
+        <v>1.4347</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0206</v>
+        <v>2.0993</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0853</v>
       </c>
       <c r="L20" t="n">
-        <v>1.936</v>
+        <v>2.014</v>
       </c>
       <c r="M20" t="n">
-        <v>0.093</v>
+        <v>-0.0207</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6633</v>
+        <v>0.5586</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5702</v>
+        <v>-0.5793</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3918</v>
+        <v>-0.4094</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4963</v>
+        <v>-0.5855</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1045</v>
+        <v>0.176</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0883</v>
+        <v>-1.9437</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4722</v>
+        <v>-3.2804</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3838</v>
+        <v>1.3367</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7991</v>
+        <v>-1.6613</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5735</v>
+        <v>0.5621</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3725</v>
+        <v>-2.2234</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0151</v>
+        <v>-0.7585</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.8384</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7696</v>
+        <v>-1.5969</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.784</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.181</v>
+        <v>-0.2763</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6029</v>
+        <v>-0.6264</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8124</v>
+        <v>-0.8137</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8111</v>
+        <v>-0.8958</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0013</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2924</v>
+        <v>0.3017</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4921</v>
+        <v>-0.4785</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7846</v>
+        <v>0.7803</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7497</v>
+        <v>-2.7615</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3532</v>
+        <v>-3.3216</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6035</v>
+        <v>0.5602</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5306</v>
+        <v>-2.534</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.417</v>
+        <v>-0.5062</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1136</v>
+        <v>-2.0279</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5542</v>
+        <v>-2.3838</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7398</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8145</v>
+        <v>-1.6777</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0237</v>
+        <v>-0.1502</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3228</v>
+        <v>0.2</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2991</v>
+        <v>-0.3502</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3882</v>
+        <v>-0.3847</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7221</v>
+        <v>-0.8723</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3339</v>
+        <v>0.4877</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2924</v>
+        <v>-0.3017</v>
       </c>
       <c r="W22" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3694</v>
+        <v>-1.3838</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3685</v>
+        <v>-3.4514</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3076</v>
+        <v>-1.3454</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.061</v>
+        <v>-2.1059</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3433</v>
+        <v>-1.4135</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4256</v>
+        <v>-1.4675</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0823</v>
+        <v>0.054</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6949</v>
+        <v>-0.6254</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5811</v>
+        <v>-1.5146</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8862</v>
+        <v>0.8892</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6484</v>
+        <v>-0.7882</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1555</v>
+        <v>0.0471</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.8353</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4867</v>
+        <v>-0.4968</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5359</v>
+        <v>-0.6546</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0491</v>
+        <v>0.1578</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W23" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.427</v>
+        <v>-4.4107</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2742</v>
+        <v>-3.2494</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1528</v>
+        <v>-1.1613</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0581</v>
+        <v>-1.0507</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6272</v>
+        <v>-0.6397</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4309</v>
+        <v>-0.411</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7167</v>
+        <v>-0.6832</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0508</v>
+        <v>0.0512</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7675</v>
+        <v>-0.7343</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3414</v>
+        <v>-0.3675</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.678</v>
+        <v>-0.6908</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3365</v>
+        <v>0.3234</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0156</v>
+        <v>0.017</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.25</v>
+        <v>-0.2712</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2656</v>
+        <v>0.2882</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.551299999999999</v>
+        <v>1.598100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>3.051700000000001</v>
+        <v>3.526200000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5007</v>
+        <v>-1.9277</v>
       </c>
       <c r="G25" t="n">
-        <v>12.5387</v>
+        <v>12.5576</v>
       </c>
       <c r="H25" t="n">
-        <v>5.013699999999999</v>
+        <v>4.542199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>7.525099999999999</v>
+        <v>8.0153</v>
       </c>
       <c r="J25" t="n">
-        <v>14.4743</v>
+        <v>15.7935</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4438</v>
+        <v>3.9391</v>
       </c>
       <c r="L25" t="n">
-        <v>11.0306</v>
+        <v>11.8546</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9355</v>
+        <v>-3.2359</v>
       </c>
       <c r="N25" t="n">
-        <v>1.5698</v>
+        <v>0.6031999999999998</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.5054</v>
+        <v>-3.8392</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0001999999999995339</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.2303</v>
+        <v>-9.18</v>
       </c>
       <c r="R25" t="n">
-        <v>9.2303</v>
+        <v>9.18</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.4564</v>
+        <v>-5.3984</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.0081</v>
+        <v>-6.936900000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5517</v>
+        <v>1.5386</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.5312</v>
+        <v>-5.5609</v>
       </c>
       <c r="W25" t="n">
-        <v>3.8159</v>
+        <v>3.8495</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.347</v>
+        <v>-9.410400000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105354_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105354_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2926</v>
+        <v>3.2294</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1334</v>
+        <v>4.8471</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8408</v>
+        <v>-1.6177</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8072</v>
+        <v>-0.8229</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5874</v>
+        <v>1.5212</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.3946</v>
+        <v>-2.3441</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2664</v>
+        <v>1.1733</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1553</v>
+        <v>1.0635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1112</v>
+        <v>0.1098</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0736</v>
+        <v>-1.9962</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4322</v>
+        <v>0.4577</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.5058</v>
+        <v>-2.4539</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1618</v>
+        <v>1.1936</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3847</v>
+        <v>0.3186</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7772</v>
+        <v>0.8749</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3969</v>
+        <v>3.3266</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6298</v>
+        <v>4.5251</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.791</v>
+        <v>2.7535</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5786</v>
+        <v>2.3401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2124</v>
+        <v>0.4134</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1257</v>
+        <v>-0.167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7702</v>
+        <v>0.709</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8959</v>
+        <v>-0.876</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6126</v>
+        <v>1.4811</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8583</v>
+        <v>0.7539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7543</v>
+        <v>0.7272</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7384</v>
+        <v>-1.6481</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0881</v>
+        <v>-0.0449</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6502</v>
+        <v>-1.6032</v>
       </c>
       <c r="P3" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4577</v>
+        <v>0.4526</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1161</v>
+        <v>-0.2051</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5737</v>
+        <v>0.6576</v>
       </c>
       <c r="V3" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W3" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,58 +736,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4649</v>
+        <v>1.5191</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8946</v>
+        <v>1.8185</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4297</v>
+        <v>-0.2994</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5313</v>
+        <v>0.5441</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0764</v>
+        <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4548</v>
+        <v>0.4656</v>
       </c>
       <c r="J4" t="n">
-        <v>1.952</v>
+        <v>1.9134</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3822</v>
+        <v>-0.3926</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3342</v>
+        <v>2.306</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4207</v>
+        <v>-1.3693</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4586</v>
+        <v>0.4711</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8793</v>
+        <v>-1.8404</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2451</v>
+        <v>0.2731</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0574</v>
+        <v>-0.0948</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3025</v>
+        <v>0.3679</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0667</v>
+        <v>1.0748</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3879</v>
+        <v>0.2337</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6788</v>
+        <v>0.8411</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5732</v>
+        <v>-1.5539</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8255</v>
+        <v>-0.8243</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7477</v>
+        <v>-0.7296</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0704</v>
+        <v>-0.1206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0711</v>
+        <v>0.0283</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1415</v>
+        <v>-0.1488</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5027</v>
+        <v>-1.4334</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8966</v>
+        <v>-0.8526</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6061</v>
+        <v>-0.5808</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2595</v>
+        <v>0.2604</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7745</v>
+        <v>-0.8442</v>
       </c>
       <c r="U5" t="n">
-        <v>1.034</v>
+        <v>1.1046</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7</v>
+        <v>0.705</v>
       </c>
       <c r="E6" t="n">
-        <v>1.627</v>
+        <v>1.5108</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.927</v>
+        <v>-0.8058</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6309</v>
+        <v>0.6172</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2876</v>
+        <v>1.2497</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6567</v>
+        <v>-0.6325</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2635</v>
+        <v>1.2114</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1524</v>
+        <v>1.1016</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1112</v>
+        <v>0.1098</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.5942</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1352</v>
+        <v>0.1481</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7678</v>
+        <v>-0.7423</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R6" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7897</v>
       </c>
       <c r="T6" t="n">
-        <v>0.429</v>
+        <v>0.4051</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3286</v>
+        <v>0.3846</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5172</v>
+        <v>0.5051</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4019</v>
+        <v>0.267</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1153</v>
+        <v>0.2381</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7186</v>
+        <v>-0.701</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.1194</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8286</v>
+        <v>-0.8204</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7281</v>
+        <v>0.6849</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1594</v>
+        <v>1.129</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4313</v>
+        <v>-0.4441</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4468</v>
+        <v>-1.3859</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0495</v>
+        <v>-1.0096</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3973</v>
+        <v>-0.3763</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R7" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3834</v>
+        <v>0.376</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2608</v>
+        <v>-0.3121</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6442</v>
+        <v>0.6881</v>
       </c>
       <c r="V7" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W7" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,40 +1068,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1179</v>
+        <v>-0.0916</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2244</v>
+        <v>-0.2623</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1065</v>
+        <v>0.1706</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6616</v>
+        <v>-0.6501</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7661</v>
+        <v>-0.7624</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1045</v>
+        <v>0.1122</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2087</v>
+        <v>-0.2232</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2458</v>
+        <v>-0.2598</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4529</v>
+        <v>-0.4269</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5203</v>
+        <v>-0.5026</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0674</v>
+        <v>0.0756</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5437</v>
+        <v>0.5585</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0156</v>
+        <v>-0.0391</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5594</v>
+        <v>0.5976</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7947</v>
+        <v>-0.8113</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8913</v>
+        <v>-0.9268</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1155</v>
       </c>
       <c r="G9" t="n">
         <v>0.268</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3151</v>
+        <v>0.311</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0471</v>
+        <v>-0.043</v>
       </c>
       <c r="J9" t="n">
-        <v>0.324</v>
+        <v>0.3155</v>
       </c>
       <c r="K9" t="n">
-        <v>0.324</v>
+        <v>0.3155</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0559</v>
+        <v>-0.0474</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0045</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0471</v>
+        <v>-0.043</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0848</v>
+        <v>0.0905</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0678</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1526</v>
+        <v>0.163</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5702</v>
+        <v>-1.5498</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4055</v>
+        <v>-1.5866</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1647</v>
+        <v>0.0368</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9271</v>
+        <v>-3.9059</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3307</v>
+        <v>-2.3432</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5964</v>
+        <v>-1.5627</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0244</v>
+        <v>-2.0725</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0985</v>
+        <v>-2.1458</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9027</v>
+        <v>-1.8334</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2322</v>
+        <v>-0.1975</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6705</v>
+        <v>-1.6359</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R10" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S10" t="n">
-        <v>0.416</v>
+        <v>0.3968</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3977</v>
+        <v>-0.4724</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8137</v>
+        <v>0.8692</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7114</v>
+        <v>1.7253</v>
       </c>
       <c r="W10" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4526</v>
+        <v>-0.4029</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8794</v>
+        <v>-1.8853</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9168</v>
+        <v>-2.0018</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0373</v>
+        <v>0.1165</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4472</v>
+        <v>-0.4185</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1711</v>
+        <v>-0.1584</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2761</v>
+        <v>-0.2601</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4322</v>
+        <v>0.4219</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3581</v>
+        <v>0.3487</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8793</v>
+        <v>-0.8404</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5291</v>
+        <v>-0.5071</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3502</v>
+        <v>-0.3333</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R11" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0365</v>
+        <v>0.0306</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4212</v>
+        <v>-0.4583</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4577</v>
+        <v>0.4889</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7803</v>
+        <v>-0.7955</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7803</v>
+        <v>-0.7955</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1723</v>
+        <v>-2.1161</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.061</v>
+        <v>-2.2123</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1113</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7578</v>
+        <v>-2.7303</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.256</v>
+        <v>-2.2418</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5018</v>
+        <v>-0.4885</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8666</v>
+        <v>-0.9252</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1767</v>
+        <v>-2.2014</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3101</v>
+        <v>1.2762</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8912</v>
+        <v>-1.8052</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0793</v>
+        <v>-0.0404</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8119</v>
+        <v>-1.7648</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R12" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8482</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0469</v>
+        <v>-0.1173</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8619</v>
+        <v>0.9655</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8961</v>
+        <v>-4.881</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5145</v>
+        <v>-2.6724</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3816</v>
+        <v>-2.2086</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.9694</v>
+        <v>-2.9699</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3395</v>
+        <v>-2.3477</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6299</v>
+        <v>-0.6222</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1728</v>
+        <v>-1.2475</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7785</v>
+        <v>-0.84</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3942</v>
+        <v>-0.4075</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7966</v>
+        <v>-1.7225</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.561</v>
+        <v>-1.5077</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2356</v>
+        <v>-0.2148</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2373</v>
+        <v>0.2172</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1943</v>
+        <v>-0.2551</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4316</v>
+        <v>0.4723</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.598199999999998</v>
+        <v>-1.548200000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0099</v>
+        <v>1.354999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.6082</v>
+        <v>-2.9033</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.5576</v>
+        <v>-12.4902</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.5422</v>
+        <v>-4.689</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.015500000000001</v>
+        <v>-7.8013</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2359</v>
+        <v>2.612499999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6031000000000006</v>
+        <v>-1.0991</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8393</v>
+        <v>3.711600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.7934</v>
+        <v>-15.1029</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.9389</v>
+        <v>-3.59</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.8544</v>
+        <v>-11.5131</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.273559366969494e-16</v>
+        <v>-2.498001805406602e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.18</v>
+        <v>-9.3592</v>
       </c>
       <c r="R14" t="n">
-        <v>9.18</v>
+        <v>9.3588</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3984</v>
+        <v>5.4872</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5386</v>
+        <v>-2.1471</v>
       </c>
       <c r="U14" t="n">
-        <v>6.937100000000001</v>
+        <v>7.634200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5609</v>
+        <v>5.454800000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4924</v>
+        <v>10.2485</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.9315</v>
+        <v>-4.7936</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0887</v>
+        <v>6.9422</v>
       </c>
       <c r="E15" t="n">
-        <v>6.6672</v>
+        <v>6.3932</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4215</v>
+        <v>0.549</v>
       </c>
       <c r="G15" t="n">
-        <v>7.0821</v>
+        <v>6.938</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7096</v>
+        <v>0.6623</v>
       </c>
       <c r="I15" t="n">
-        <v>6.3725</v>
+        <v>6.2757</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3205</v>
+        <v>7.1162</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4832</v>
+        <v>0.3886</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8373</v>
+        <v>6.7276</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2383</v>
+        <v>-0.1782</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2264</v>
+        <v>0.2737</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4648</v>
+        <v>-0.4519</v>
       </c>
       <c r="P15" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4525</v>
+        <v>-0.4638</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6533</v>
+        <v>-0.723</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2008</v>
+        <v>0.2593</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1126</v>
+        <v>3.146</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8714</v>
+        <v>2.6367</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2412</v>
+        <v>0.5093</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6128</v>
+        <v>4.6244</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8004</v>
+        <v>1.8514</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8124</v>
+        <v>2.773</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8925</v>
+        <v>4.8014</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9889</v>
+        <v>0.963</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9036</v>
+        <v>3.8384</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2797</v>
+        <v>-0.177</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8115</v>
+        <v>0.8884</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0912</v>
+        <v>-1.0654</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R16" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9558</v>
+        <v>-0.9819</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8736</v>
+        <v>-0.9948</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.0129</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3142</v>
+        <v>2.2694</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0995</v>
+        <v>2.8893</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7853</v>
+        <v>-0.62</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3547</v>
+        <v>2.3098</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.077</v>
+        <v>-0.0709</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4317</v>
+        <v>2.3807</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9811</v>
+        <v>2.863</v>
       </c>
       <c r="K17" t="n">
-        <v>0.361</v>
+        <v>0.3105</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6202</v>
+        <v>2.5525</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.5532</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.438</v>
+        <v>-0.3814</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1885</v>
+        <v>-0.1718</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1879</v>
+        <v>-1.2102</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9636</v>
+        <v>-1.0378</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2243</v>
+        <v>-0.1725</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0996</v>
+        <v>2.0982</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4211</v>
+        <v>1.2512</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6785</v>
+        <v>0.847</v>
       </c>
       <c r="G18" t="n">
-        <v>2.32</v>
+        <v>2.2973</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9932</v>
+        <v>1.9654</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3268</v>
+        <v>0.3319</v>
       </c>
       <c r="J18" t="n">
-        <v>2.179</v>
+        <v>2.105</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9196</v>
+        <v>1.8488</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2594</v>
+        <v>0.2562</v>
       </c>
       <c r="M18" t="n">
-        <v>0.141</v>
+        <v>0.1923</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0735</v>
+        <v>0.1166</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0674</v>
+        <v>0.0756</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2204</v>
+        <v>-0.1991</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6924</v>
+        <v>-0.748</v>
       </c>
       <c r="U18" t="n">
-        <v>0.472</v>
+        <v>0.549</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5042</v>
+        <v>0.5239</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2974</v>
+        <v>0.2263</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2069</v>
+        <v>0.2975</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7689</v>
+        <v>0.7731</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5234</v>
+        <v>1.5203</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7472</v>
       </c>
       <c r="J19" t="n">
-        <v>0.772</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4322</v>
+        <v>1.3946</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6602</v>
+        <v>-0.6613</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0031</v>
+        <v>0.0397</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0912</v>
+        <v>0.1256</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0859</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4942</v>
+        <v>-0.4832</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4746</v>
+        <v>-0.507</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0196</v>
+        <v>0.0239</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9539</v>
+        <v>-0.9397</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3664</v>
+        <v>0.2342</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3202</v>
+        <v>-1.174</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0786</v>
+        <v>2.0854</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6439</v>
+        <v>0.6843</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4347</v>
+        <v>1.4012</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0993</v>
+        <v>2.0547</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0853</v>
+        <v>0.083</v>
       </c>
       <c r="L20" t="n">
-        <v>2.014</v>
+        <v>1.9717</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0207</v>
+        <v>0.0307</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5586</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5793</v>
+        <v>-0.5705</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4094</v>
+        <v>-0.429</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5855</v>
+        <v>-0.6506</v>
       </c>
       <c r="U20" t="n">
-        <v>0.176</v>
+        <v>0.2216</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9437</v>
+        <v>-2.0109</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2804</v>
+        <v>-3.5094</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3367</v>
+        <v>1.4985</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6613</v>
+        <v>-1.6806</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5621</v>
+        <v>0.5555</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2234</v>
+        <v>-2.2362</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7585</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8384</v>
+        <v>0.7754</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5969</v>
+        <v>-1.6227</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.8334</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2763</v>
+        <v>-0.2199</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6264</v>
+        <v>-0.6135</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R21" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8137</v>
+        <v>-0.8328</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8958</v>
+        <v>-0.9653</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1325</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4785</v>
+        <v>-0.5269</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7803</v>
+        <v>0.7955</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7615</v>
+        <v>-2.6667</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3216</v>
+        <v>-3.4867</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5602</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.534</v>
+        <v>-2.4746</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5062</v>
+        <v>-0.4478</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0279</v>
+        <v>-2.0268</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3838</v>
+        <v>-2.4015</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7081</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6777</v>
+        <v>-1.6935</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1502</v>
+        <v>-0.0731</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2</v>
+        <v>0.2602</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3502</v>
+        <v>-0.3333</v>
       </c>
       <c r="P22" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3847</v>
+        <v>-0.3913</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8723</v>
+        <v>-0.9794</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4877</v>
+        <v>0.5881</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3017</v>
+        <v>-0.2686</v>
       </c>
       <c r="W22" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3838</v>
+        <v>-1.3327</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4514</v>
+        <v>-3.3981</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3454</v>
+        <v>-1.4815</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1059</v>
+        <v>-1.9166</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4135</v>
+        <v>-1.3521</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4675</v>
+        <v>-1.4126</v>
       </c>
       <c r="I23" t="n">
-        <v>0.054</v>
+        <v>0.0605</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6254</v>
+        <v>-0.6373</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5146</v>
+        <v>-1.5158</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8892</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7882</v>
+        <v>-0.7148</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0471</v>
+        <v>0.1032</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8353</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4968</v>
+        <v>-0.5139</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6546</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1578</v>
+        <v>0.2245</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W23" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4107</v>
+        <v>-4.4159</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2494</v>
+        <v>-3.3141</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1613</v>
+        <v>-1.1018</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0507</v>
+        <v>-1.0302</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6397</v>
+        <v>-0.6188</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.411</v>
+        <v>-0.4114</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6832</v>
+        <v>-0.6847</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0512</v>
+        <v>0.0498</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7343</v>
+        <v>-0.7345</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3675</v>
+        <v>-0.3455</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6908</v>
+        <v>-0.6686</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3234</v>
+        <v>0.3231</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.017</v>
+        <v>0.0181</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2712</v>
+        <v>-0.2897</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2882</v>
+        <v>0.3078</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.598100000000001</v>
+        <v>1.548400000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>3.526200000000001</v>
+        <v>1.8392</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9277</v>
+        <v>-0.2910000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>12.5576</v>
+        <v>12.4905</v>
       </c>
       <c r="H25" t="n">
-        <v>4.542199999999999</v>
+        <v>4.689099999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>8.0153</v>
+        <v>7.801399999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>15.7935</v>
+        <v>15.1029</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9391</v>
+        <v>3.589799999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>11.8546</v>
+        <v>11.5129</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.2359</v>
+        <v>-2.6125</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6031999999999998</v>
+        <v>1.0991</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.8392</v>
+        <v>-3.7116</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>9.999999999932285e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.18</v>
+        <v>-9.3591</v>
       </c>
       <c r="R25" t="n">
-        <v>9.18</v>
+        <v>9.3589</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.3984</v>
+        <v>-5.487100000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.936900000000001</v>
+        <v>-7.634</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5386</v>
+        <v>2.1471</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.5609</v>
+        <v>-5.4548</v>
       </c>
       <c r="W25" t="n">
-        <v>3.8495</v>
+        <v>3.7295</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.410400000000001</v>
+        <v>-9.1843</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105354_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105354_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2294</v>
+        <v>3.2616</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8471</v>
+        <v>4.9808</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6177</v>
+        <v>-1.7191</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8229</v>
+        <v>-0.8062</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5212</v>
+        <v>1.5393</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.3441</v>
+        <v>-2.3455</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1733</v>
+        <v>1.1878</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0635</v>
+        <v>1.0774</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1098</v>
+        <v>0.1104</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9962</v>
+        <v>-1.994</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4577</v>
+        <v>0.4619</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.4539</v>
+        <v>-2.4559</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1936</v>
+        <v>1.1755</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3186</v>
+        <v>0.3838</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8749</v>
+        <v>0.7916</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3266</v>
+        <v>3.3565</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5251</v>
+        <v>4.5695</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7535</v>
+        <v>2.7681</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3401</v>
+        <v>2.4351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4134</v>
+        <v>0.333</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.167</v>
+        <v>-0.1578</v>
       </c>
       <c r="H3" t="n">
-        <v>0.709</v>
+        <v>0.7183</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.876</v>
+        <v>-0.8761</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4811</v>
+        <v>1.4868</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7539</v>
+        <v>0.7648</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7272</v>
+        <v>0.722</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6481</v>
+        <v>-1.6446</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0449</v>
+        <v>-0.0465</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6032</v>
+        <v>-1.5981</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4526</v>
+        <v>0.4618</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2051</v>
+        <v>-0.1234</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6576</v>
+        <v>0.5853</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,58 +736,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5191</v>
+        <v>1.5011</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8185</v>
+        <v>1.8608</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2994</v>
+        <v>-0.3598</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5441</v>
+        <v>0.5554</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0785</v>
+        <v>0.0793</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4656</v>
+        <v>0.4761</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9134</v>
+        <v>1.9214</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3926</v>
+        <v>-0.3965</v>
       </c>
       <c r="L4" t="n">
-        <v>2.306</v>
+        <v>2.3179</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3693</v>
+        <v>-1.366</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4711</v>
+        <v>0.4759</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8404</v>
+        <v>-1.8419</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2731</v>
+        <v>0.2495</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0948</v>
+        <v>-0.0606</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3679</v>
+        <v>0.3101</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0748</v>
+        <v>1.0734</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2337</v>
+        <v>0.3017</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8411</v>
+        <v>0.7718</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5539</v>
+        <v>-1.5621</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8243</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7296</v>
+        <v>-0.7289</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1206</v>
+        <v>-0.1243</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0283</v>
+        <v>0.0298</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1488</v>
+        <v>-0.1541</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4334</v>
+        <v>-1.4377</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8526</v>
+        <v>-0.8629</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5808</v>
+        <v>-0.5748</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2604</v>
+        <v>0.2621</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8442</v>
+        <v>-0.787</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1046</v>
+        <v>1.0492</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.705</v>
+        <v>0.7075</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5108</v>
+        <v>1.5681</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8058</v>
+        <v>-0.8606</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6172</v>
+        <v>0.6364</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2497</v>
+        <v>1.2641</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6325</v>
+        <v>-0.6277</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2114</v>
+        <v>1.2252</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1016</v>
+        <v>1.1148</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1098</v>
+        <v>0.1104</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5942</v>
+        <v>-0.5888</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1481</v>
+        <v>0.1493</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7423</v>
+        <v>-0.7381</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7897</v>
+        <v>0.7673</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4051</v>
+        <v>0.4316</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3846</v>
+        <v>0.3357</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5051</v>
+        <v>0.5211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.267</v>
+        <v>0.331</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2381</v>
+        <v>0.1901</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.701</v>
+        <v>-0.7052</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1194</v>
+        <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8204</v>
+        <v>-0.8255</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6849</v>
+        <v>0.6865</v>
       </c>
       <c r="K7" t="n">
-        <v>1.129</v>
+        <v>1.1419</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4441</v>
+        <v>-0.4554</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3859</v>
+        <v>-1.3917</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0096</v>
+        <v>-1.0215</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3763</v>
+        <v>-0.3702</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S7" t="n">
-        <v>0.376</v>
+        <v>0.3866</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3121</v>
+        <v>-0.2669</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6881</v>
+        <v>0.6536</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,40 +1068,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0916</v>
+        <v>-0.1032</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2623</v>
+        <v>-0.2429</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1706</v>
+        <v>0.1397</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6501</v>
+        <v>-0.6533</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7624</v>
+        <v>-0.7706</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1122</v>
+        <v>0.1173</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2232</v>
+        <v>-0.2254</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2598</v>
+        <v>-0.2622</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0366</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4269</v>
+        <v>-0.4279</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5026</v>
+        <v>-0.5084</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0756</v>
+        <v>0.0805</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5585</v>
+        <v>0.5501</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0391</v>
+        <v>-0.0174</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5976</v>
+        <v>0.5676</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8113</v>
+        <v>-0.8013</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9268</v>
+        <v>-0.9101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1155</v>
+        <v>0.1088</v>
       </c>
       <c r="G9" t="n">
-        <v>0.268</v>
+        <v>0.273</v>
       </c>
       <c r="H9" t="n">
-        <v>0.311</v>
+        <v>0.3144</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.043</v>
+        <v>-0.0414</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3155</v>
+        <v>0.3191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3155</v>
+        <v>0.3191</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0474</v>
+        <v>-0.046</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.043</v>
+        <v>-0.0414</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0905</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0688</v>
       </c>
       <c r="U9" t="n">
-        <v>0.163</v>
+        <v>0.1548</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5498</v>
+        <v>-1.5614</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5866</v>
+        <v>-1.5177</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0368</v>
+        <v>-0.0438</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9059</v>
+        <v>-3.9316</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3432</v>
+        <v>-2.368</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5627</v>
+        <v>-1.5637</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0725</v>
+        <v>-2.0939</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1458</v>
+        <v>-2.1675</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0732</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8334</v>
+        <v>-1.8377</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1975</v>
+        <v>-0.2005</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6359</v>
+        <v>-1.6372</v>
       </c>
       <c r="P10" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3968</v>
+        <v>0.4187</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4724</v>
+        <v>-0.4068</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8692</v>
+        <v>0.8256</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7253</v>
+        <v>1.7194</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4029</v>
+        <v>-0.424</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8853</v>
+        <v>-1.8645</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0018</v>
+        <v>-1.9511</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1165</v>
+        <v>0.0866</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4185</v>
+        <v>-0.4157</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1584</v>
+        <v>-0.1604</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2601</v>
+        <v>-0.2552</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4219</v>
+        <v>0.4262</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3487</v>
+        <v>0.3526</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0732</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8404</v>
+        <v>-0.8419</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5071</v>
+        <v>-0.5131</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3333</v>
+        <v>-0.3288</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0306</v>
+        <v>0.0365</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4583</v>
+        <v>-0.4279</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4889</v>
+        <v>0.4644</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7955</v>
+        <v>-0.789</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7955</v>
+        <v>-0.789</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1161</v>
+        <v>-2.1604</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2123</v>
+        <v>-2.1631</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0027</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7303</v>
+        <v>-2.7537</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2418</v>
+        <v>-2.2662</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4885</v>
+        <v>-0.4875</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9252</v>
+        <v>-0.9504</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2014</v>
+        <v>-2.2243</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2762</v>
+        <v>1.2739</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8052</v>
+        <v>-1.8033</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0404</v>
+        <v>-0.0419</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7648</v>
+        <v>-1.7614</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8482</v>
+        <v>0.8253</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1173</v>
+        <v>-0.0523</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9655</v>
+        <v>0.8776</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.881</v>
+        <v>-4.9033</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6724</v>
+        <v>-2.6267</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2086</v>
+        <v>-2.2766</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.9699</v>
+        <v>-2.9981</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3477</v>
+        <v>-2.3726</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6222</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2475</v>
+        <v>-1.2659</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.84</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4075</v>
+        <v>-0.4186</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7225</v>
+        <v>-1.7322</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5077</v>
+        <v>-1.5253</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2148</v>
+        <v>-0.2069</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2172</v>
+        <v>0.2383</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2551</v>
+        <v>-0.2005</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4723</v>
+        <v>0.4387</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.548200000000002</v>
+        <v>-1.5613</v>
       </c>
       <c r="E14" t="n">
-        <v>1.354999999999999</v>
+        <v>2.065900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9033</v>
+        <v>-3.6272</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.4902</v>
+        <v>-12.5189</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.689</v>
+        <v>-4.735199999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.8013</v>
+        <v>-7.7836</v>
       </c>
       <c r="J14" t="n">
-        <v>2.612499999999999</v>
+        <v>2.5931</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.0991</v>
+        <v>-1.097399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>3.711600000000001</v>
+        <v>3.6905</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.1029</v>
+        <v>-15.1118</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.59</v>
+        <v>-3.6377</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.5131</v>
+        <v>-11.4742</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.498001805406602e-16</v>
+        <v>8.326672684688674e-17</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.3592</v>
+        <v>-9.283200000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>9.3588</v>
+        <v>9.282800000000002</v>
       </c>
       <c r="S14" t="n">
-        <v>5.4872</v>
+        <v>5.457700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1471</v>
+        <v>-1.5962</v>
       </c>
       <c r="U14" t="n">
-        <v>7.634200000000001</v>
+        <v>7.054200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>5.454800000000001</v>
+        <v>5.4999</v>
       </c>
       <c r="W14" t="n">
-        <v>10.2485</v>
+        <v>10.352</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.7936</v>
+        <v>-4.8521</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9422</v>
+        <v>6.9755</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3932</v>
+        <v>6.4799</v>
       </c>
       <c r="F15" t="n">
-        <v>0.549</v>
+        <v>0.4957</v>
       </c>
       <c r="G15" t="n">
-        <v>6.938</v>
+        <v>6.9691</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6623</v>
+        <v>0.6707</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2757</v>
+        <v>6.2984</v>
       </c>
       <c r="J15" t="n">
-        <v>7.1162</v>
+        <v>7.1445</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3886</v>
+        <v>0.3954</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7276</v>
+        <v>6.7491</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1782</v>
+        <v>-0.1753</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2737</v>
+        <v>0.2753</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4519</v>
+        <v>-0.4507</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4638</v>
+        <v>-0.4577</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.723</v>
+        <v>-0.6646</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2593</v>
+        <v>0.2069</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.146</v>
+        <v>3.1707</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6367</v>
+        <v>2.7723</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5093</v>
+        <v>0.3984</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6244</v>
+        <v>4.6546</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8514</v>
+        <v>1.8698</v>
       </c>
       <c r="I16" t="n">
-        <v>2.773</v>
+        <v>2.7847</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8014</v>
+        <v>4.8234</v>
       </c>
       <c r="K16" t="n">
-        <v>0.963</v>
+        <v>0.974</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8384</v>
+        <v>3.8494</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.177</v>
+        <v>-0.1688</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8884</v>
+        <v>0.8959</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0654</v>
+        <v>-1.0647</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9819</v>
+        <v>-0.967</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9948</v>
+        <v>-0.8907</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0129</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2694</v>
+        <v>2.2696</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8893</v>
+        <v>2.9564</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.62</v>
+        <v>-0.6868</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3098</v>
+        <v>2.3104</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0709</v>
+        <v>-0.0718</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3807</v>
+        <v>2.3823</v>
       </c>
       <c r="J17" t="n">
         <v>2.863</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3105</v>
+        <v>0.3152</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5525</v>
+        <v>2.5478</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5532</v>
+        <v>-0.5526</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3814</v>
+        <v>-0.3871</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1718</v>
+        <v>-0.1655</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2102</v>
+        <v>-1.2012</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0378</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1725</v>
+        <v>-0.2229</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0982</v>
+        <v>2.1042</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2512</v>
+        <v>1.3363</v>
       </c>
       <c r="F18" t="n">
-        <v>0.847</v>
+        <v>0.7679</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2973</v>
+        <v>2.3253</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9654</v>
+        <v>1.9872</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3319</v>
+        <v>0.3381</v>
       </c>
       <c r="J18" t="n">
-        <v>2.105</v>
+        <v>2.128</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8488</v>
+        <v>1.8705</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2562</v>
+        <v>0.2575</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1923</v>
+        <v>0.1972</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1166</v>
+        <v>0.1167</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0756</v>
+        <v>0.0805</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1991</v>
+        <v>-0.2211</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.748</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.549</v>
+        <v>0.4821</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5239</v>
+        <v>0.5184</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2263</v>
+        <v>0.2598</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2975</v>
+        <v>0.2586</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7731</v>
+        <v>0.7847</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5203</v>
+        <v>1.5366</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7472</v>
+        <v>-0.752</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3946</v>
+        <v>1.4106</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6613</v>
+        <v>-0.6692</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0397</v>
+        <v>0.0433</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1256</v>
+        <v>0.126</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0859</v>
+        <v>-0.0828</v>
       </c>
       <c r="P19" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4832</v>
+        <v>-0.4983</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.507</v>
+        <v>-0.4816</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0239</v>
+        <v>-0.0167</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9397</v>
+        <v>-0.9315</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2342</v>
+        <v>0.3008</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.174</v>
+        <v>-1.2323</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0854</v>
+        <v>2.0909</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6843</v>
+        <v>0.6905</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4012</v>
+        <v>1.4004</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0547</v>
+        <v>2.0569</v>
       </c>
       <c r="K20" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9717</v>
+        <v>1.973</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0307</v>
+        <v>0.034</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6066</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5705</v>
+        <v>-0.5726</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.429</v>
+        <v>-0.4148</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6506</v>
+        <v>-0.5958</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2216</v>
+        <v>0.181</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0109</v>
+        <v>-2.0141</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5094</v>
+        <v>-3.4443</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4985</v>
+        <v>1.4302</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6806</v>
+        <v>-1.7058</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5555</v>
+        <v>0.5616</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2362</v>
+        <v>-2.2675</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.8681</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7754</v>
+        <v>0.7854</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6227</v>
+        <v>-1.6535</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8334</v>
+        <v>-0.8377</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2199</v>
+        <v>-0.2238</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6135</v>
+        <v>-0.614</v>
       </c>
       <c r="P21" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8328</v>
+        <v>-0.823</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9653</v>
+        <v>-0.9095</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1325</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.5269</v>
+        <v>-0.5064</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7955</v>
+        <v>0.789</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6667</v>
+        <v>-2.7107</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4867</v>
+        <v>-3.4129</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.7022</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4746</v>
+        <v>-2.5032</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4478</v>
+        <v>-0.4542</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0268</v>
+        <v>-2.049</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4015</v>
+        <v>-2.4358</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7081</v>
+        <v>-0.7156</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6935</v>
+        <v>-1.7202</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0731</v>
+        <v>-0.0674</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2602</v>
+        <v>0.2614</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3333</v>
+        <v>-0.3288</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3913</v>
+        <v>-0.3889</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9794</v>
+        <v>-0.8884</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5881</v>
+        <v>0.4995</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2686</v>
+        <v>-0.2827</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3327</v>
+        <v>-1.3544</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3981</v>
+        <v>-3.4036</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4815</v>
+        <v>-1.4045</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9166</v>
+        <v>-1.9991</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3521</v>
+        <v>-1.3648</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4126</v>
+        <v>-1.4292</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0605</v>
+        <v>0.0644</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6373</v>
+        <v>-0.649</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5158</v>
+        <v>-1.532</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.883</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7148</v>
+        <v>-0.7159</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1032</v>
+        <v>0.1028</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.8186</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5139</v>
+        <v>-0.5029</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.6669</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2245</v>
+        <v>0.164</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4159</v>
+        <v>-4.4175</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3141</v>
+        <v>-3.2883</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1018</v>
+        <v>-1.1291</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0302</v>
+        <v>-1.0422</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6188</v>
+        <v>-0.626</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4114</v>
+        <v>-0.4162</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6847</v>
+        <v>-0.6924</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0498</v>
+        <v>0.0504</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7345</v>
+        <v>-0.7428</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3455</v>
+        <v>-0.3498</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6686</v>
+        <v>-0.6764</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3231</v>
+        <v>0.3265</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0181</v>
+        <v>0.0172</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2897</v>
+        <v>-0.2752</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3078</v>
+        <v>0.2924</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.548400000000002</v>
+        <v>1.560999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8392</v>
+        <v>2.5555</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2910000000000001</v>
+        <v>-0.9943</v>
       </c>
       <c r="G25" t="n">
-        <v>12.4905</v>
+        <v>12.519</v>
       </c>
       <c r="H25" t="n">
-        <v>4.689099999999999</v>
+        <v>4.7352</v>
       </c>
       <c r="I25" t="n">
-        <v>7.801399999999999</v>
+        <v>7.7836</v>
       </c>
       <c r="J25" t="n">
-        <v>15.1029</v>
+        <v>15.1119</v>
       </c>
       <c r="K25" t="n">
-        <v>3.589799999999999</v>
+        <v>3.6379</v>
       </c>
       <c r="L25" t="n">
-        <v>11.5129</v>
+        <v>11.4741</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6125</v>
+        <v>-2.593</v>
       </c>
       <c r="N25" t="n">
-        <v>1.0991</v>
+        <v>1.0974</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.7116</v>
+        <v>-3.6907</v>
       </c>
       <c r="P25" t="n">
-        <v>9.999999999932285e-05</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.3591</v>
+        <v>-9.283100000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>9.3589</v>
+        <v>9.2829</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.487100000000001</v>
+        <v>-5.457700000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.634</v>
+        <v>-7.0541</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1471</v>
+        <v>1.5965</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.4548</v>
+        <v>-5.4998</v>
       </c>
       <c r="W25" t="n">
-        <v>3.7295</v>
+        <v>3.7804</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.1843</v>
+        <v>-9.2803</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>
